--- a/Matlab - Simulink/Resultados_transitorios.xlsx
+++ b/Matlab - Simulink/Resultados_transitorios.xlsx
@@ -15,126 +15,246 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="40">
-  <si>
-    <t>Perturbacion_s</t>
-  </si>
-  <si>
-    <t>RiseTimeFallTime_ms</t>
-  </si>
-  <si>
-    <t>SettlingTime_ms</t>
-  </si>
-  <si>
-    <t>OverUnder_pct</t>
-  </si>
-  <si>
-    <t>ValorEstablecimiento</t>
-  </si>
-  <si>
-    <t>Perturbacion_s</t>
-  </si>
-  <si>
-    <t>RiseTimeFallTime_ms</t>
-  </si>
-  <si>
-    <t>SettlingTime_ms</t>
-  </si>
-  <si>
-    <t>OverUnder_pct</t>
-  </si>
-  <si>
-    <t>ValorEstablecimiento</t>
-  </si>
-  <si>
-    <t>Perturbacion_s</t>
-  </si>
-  <si>
-    <t>RiseTimeFallTime_ms</t>
-  </si>
-  <si>
-    <t>SettlingTime_ms</t>
-  </si>
-  <si>
-    <t>OverUnder_pct</t>
-  </si>
-  <si>
-    <t>ValorEstablecimiento</t>
-  </si>
-  <si>
-    <t>Perturbacion_s</t>
-  </si>
-  <si>
-    <t>RiseTimeFallTime_ms</t>
-  </si>
-  <si>
-    <t>SettlingTime_ms</t>
-  </si>
-  <si>
-    <t>OverUnder_pct</t>
-  </si>
-  <si>
-    <t>ValorEstablecimiento</t>
-  </si>
-  <si>
-    <t>Perturbacion_s</t>
-  </si>
-  <si>
-    <t>RiseFall_ms</t>
-  </si>
-  <si>
-    <t>Settling_ms</t>
-  </si>
-  <si>
-    <t>OverUnder_pct</t>
-  </si>
-  <si>
-    <t>ValorEstab</t>
-  </si>
-  <si>
-    <t>Perturbacion_s</t>
-  </si>
-  <si>
-    <t>RiseFall_ms</t>
-  </si>
-  <si>
-    <t>Settling_ms</t>
-  </si>
-  <si>
-    <t>OverUnder_pct</t>
-  </si>
-  <si>
-    <t>ValorEstab</t>
-  </si>
-  <si>
-    <t>Perturbacion_s</t>
-  </si>
-  <si>
-    <t>RiseFall_ms</t>
-  </si>
-  <si>
-    <t>Settling_ms</t>
-  </si>
-  <si>
-    <t>OverUnder_pct</t>
-  </si>
-  <si>
-    <t>ValorEstab</t>
-  </si>
-  <si>
-    <t>Perturbacion_s</t>
-  </si>
-  <si>
-    <t>RiseFall_ms</t>
-  </si>
-  <si>
-    <t>Settling_ms</t>
-  </si>
-  <si>
-    <t>OverUnder_pct</t>
-  </si>
-  <si>
-    <t>ValorEstab</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="80">
+  <si>
+    <t>Perturbacion_s</t>
+  </si>
+  <si>
+    <t>RiseTimeFallTime_ms</t>
+  </si>
+  <si>
+    <t>SettlingTime_ms</t>
+  </si>
+  <si>
+    <t>OverUnder_pct</t>
+  </si>
+  <si>
+    <t>ValorEstablecimiento</t>
+  </si>
+  <si>
+    <t>Perturbacion_s</t>
+  </si>
+  <si>
+    <t>RiseTimeFallTime_ms</t>
+  </si>
+  <si>
+    <t>SettlingTime_ms</t>
+  </si>
+  <si>
+    <t>OverUnder_pct</t>
+  </si>
+  <si>
+    <t>ValorEstablecimiento</t>
+  </si>
+  <si>
+    <t>Perturbacion_s</t>
+  </si>
+  <si>
+    <t>RiseTimeFallTime_ms</t>
+  </si>
+  <si>
+    <t>SettlingTime_ms</t>
+  </si>
+  <si>
+    <t>OverUnder_pct</t>
+  </si>
+  <si>
+    <t>ValorEstablecimiento</t>
+  </si>
+  <si>
+    <t>Perturbacion_s</t>
+  </si>
+  <si>
+    <t>RiseTimeFallTime_ms</t>
+  </si>
+  <si>
+    <t>SettlingTime_ms</t>
+  </si>
+  <si>
+    <t>OverUnder_pct</t>
+  </si>
+  <si>
+    <t>ValorEstablecimiento</t>
+  </si>
+  <si>
+    <t>Perturbacion_s</t>
+  </si>
+  <si>
+    <t>RiseTimeFallTime_ms</t>
+  </si>
+  <si>
+    <t>SettlingTime_ms</t>
+  </si>
+  <si>
+    <t>OverUnder_pct</t>
+  </si>
+  <si>
+    <t>ValorEstablecimiento</t>
+  </si>
+  <si>
+    <t>Perturbacion_s</t>
+  </si>
+  <si>
+    <t>RiseTimeFallTime_ms</t>
+  </si>
+  <si>
+    <t>SettlingTime_ms</t>
+  </si>
+  <si>
+    <t>OverUnder_pct</t>
+  </si>
+  <si>
+    <t>ValorEstablecimiento</t>
+  </si>
+  <si>
+    <t>Perturbacion_s</t>
+  </si>
+  <si>
+    <t>RiseTimeFallTime_ms</t>
+  </si>
+  <si>
+    <t>SettlingTime_ms</t>
+  </si>
+  <si>
+    <t>OverUnder_pct</t>
+  </si>
+  <si>
+    <t>ValorEstablecimiento</t>
+  </si>
+  <si>
+    <t>Perturbacion_s</t>
+  </si>
+  <si>
+    <t>RiseTimeFallTime_ms</t>
+  </si>
+  <si>
+    <t>SettlingTime_ms</t>
+  </si>
+  <si>
+    <t>OverUnder_pct</t>
+  </si>
+  <si>
+    <t>ValorEstablecimiento</t>
+  </si>
+  <si>
+    <t>Perturbacion_s</t>
+  </si>
+  <si>
+    <t>RiseTimeFallTime_ms</t>
+  </si>
+  <si>
+    <t>SettlingTime_ms</t>
+  </si>
+  <si>
+    <t>OverUnder_pct</t>
+  </si>
+  <si>
+    <t>ValorEstablecimiento</t>
+  </si>
+  <si>
+    <t>Perturbacion_s</t>
+  </si>
+  <si>
+    <t>RiseTimeFallTime_ms</t>
+  </si>
+  <si>
+    <t>SettlingTime_ms</t>
+  </si>
+  <si>
+    <t>OverUnder_pct</t>
+  </si>
+  <si>
+    <t>ValorEstablecimiento</t>
+  </si>
+  <si>
+    <t>Perturbacion_s</t>
+  </si>
+  <si>
+    <t>RiseTimeFallTime_ms</t>
+  </si>
+  <si>
+    <t>SettlingTime_ms</t>
+  </si>
+  <si>
+    <t>OverUnder_pct</t>
+  </si>
+  <si>
+    <t>ValorEstablecimiento</t>
+  </si>
+  <si>
+    <t>Perturbacion_s</t>
+  </si>
+  <si>
+    <t>RiseTimeFallTime_ms</t>
+  </si>
+  <si>
+    <t>SettlingTime_ms</t>
+  </si>
+  <si>
+    <t>OverUnder_pct</t>
+  </si>
+  <si>
+    <t>ValorEstablecimiento</t>
+  </si>
+  <si>
+    <t>Perturbacion_s</t>
+  </si>
+  <si>
+    <t>RiseTimeFallTime_ms</t>
+  </si>
+  <si>
+    <t>SettlingTime_ms</t>
+  </si>
+  <si>
+    <t>OverUnder_pct</t>
+  </si>
+  <si>
+    <t>ValorEstablecimiento</t>
+  </si>
+  <si>
+    <t>Perturbacion_s</t>
+  </si>
+  <si>
+    <t>RiseTimeFallTime_ms</t>
+  </si>
+  <si>
+    <t>SettlingTime_ms</t>
+  </si>
+  <si>
+    <t>OverUnder_pct</t>
+  </si>
+  <si>
+    <t>ValorEstablecimiento</t>
+  </si>
+  <si>
+    <t>Perturbacion_s</t>
+  </si>
+  <si>
+    <t>RiseTimeFallTime_ms</t>
+  </si>
+  <si>
+    <t>SettlingTime_ms</t>
+  </si>
+  <si>
+    <t>OverUnder_pct</t>
+  </si>
+  <si>
+    <t>ValorEstablecimiento</t>
+  </si>
+  <si>
+    <t>Perturbacion_s</t>
+  </si>
+  <si>
+    <t>RiseTimeFallTime_ms</t>
+  </si>
+  <si>
+    <t>SettlingTime_ms</t>
+  </si>
+  <si>
+    <t>OverUnder_pct</t>
+  </si>
+  <si>
+    <t>ValorEstablecimiento</t>
   </si>
 </sst>
 </file>
@@ -184,27 +304,27 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="14.42578125" customWidth="true"/>
-    <col min="2" max="2" width="11.7109375" customWidth="true"/>
-    <col min="3" max="3" width="11.7109375" customWidth="true"/>
+    <col min="2" max="2" width="20.42578125" customWidth="true"/>
+    <col min="3" max="3" width="16" customWidth="true"/>
     <col min="4" max="4" width="14.5703125" customWidth="true"/>
-    <col min="5" max="5" width="12.42578125" customWidth="true"/>
+    <col min="5" max="5" width="20.140625" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="0" t="s">
-        <v>30</v>
+        <v>70</v>
       </c>
       <c r="B1" s="0" t="s">
-        <v>31</v>
+        <v>71</v>
       </c>
       <c r="C1" s="0" t="s">
-        <v>32</v>
+        <v>72</v>
       </c>
       <c r="D1" s="0" t="s">
-        <v>33</v>
+        <v>73</v>
       </c>
       <c r="E1" s="0" t="s">
-        <v>34</v>
+        <v>74</v>
       </c>
     </row>
     <row r="2">
@@ -218,10 +338,10 @@
         <v>68.296958268147435</v>
       </c>
       <c r="D2" s="0">
-        <v>22.97096485117779</v>
+        <v>22.992237867147455</v>
       </c>
       <c r="E2" s="0">
-        <v>403.00083143125107</v>
+        <v>402.93112749487676</v>
       </c>
     </row>
     <row r="3">
@@ -232,13 +352,13 @@
         <v>6.0000000000000053</v>
       </c>
       <c r="C3" s="0">
-        <v>163.2969582681477</v>
+        <v>168.29695826814773</v>
       </c>
       <c r="D3" s="0">
-        <v>27.125908986624321</v>
+        <v>26.975668092174399</v>
       </c>
       <c r="E3" s="0">
-        <v>387.98594238010571</v>
+        <v>387.96095430764603</v>
       </c>
     </row>
     <row r="4">
@@ -249,13 +369,13 @@
         <v>4.6358615911107348</v>
       </c>
       <c r="C4" s="0">
-        <v>143.56868145036927</v>
+        <v>151.56868145036927</v>
       </c>
       <c r="D4" s="0">
-        <v>42.241374688939118</v>
+        <v>42.041126807213431</v>
       </c>
       <c r="E4" s="0">
-        <v>414.403702184471</v>
+        <v>414.43747125144449</v>
       </c>
     </row>
     <row r="5">
@@ -269,10 +389,10 @@
         <v>61.59234523577728</v>
       </c>
       <c r="D5" s="0">
-        <v>21.666971558671779</v>
+        <v>21.666403297957356</v>
       </c>
       <c r="E5" s="0">
-        <v>8.6082898601668472</v>
+        <v>8.6094025853890876</v>
       </c>
     </row>
     <row r="6">
@@ -286,10 +406,10 @@
         <v>60.592345235777387</v>
       </c>
       <c r="D6" s="0">
-        <v>41.793738830366003</v>
+        <v>41.787102165869236</v>
       </c>
       <c r="E6" s="0">
-        <v>-4.6667055546630696</v>
+        <v>-4.667170933662784</v>
       </c>
     </row>
     <row r="7">
@@ -303,10 +423,10 @@
         <v>51.15442229711276</v>
       </c>
       <c r="D7" s="0">
-        <v>21.172217547441182</v>
+        <v>21.177278728232718</v>
       </c>
       <c r="E7" s="0">
-        <v>-411.09364140168026</v>
+        <v>-411.07670583531336</v>
       </c>
     </row>
     <row r="8">
@@ -317,13 +437,13 @@
         <v>3.9999999999995595</v>
       </c>
       <c r="C8" s="0">
-        <v>199.99999999999994</v>
+        <v>187.1544222970758</v>
       </c>
       <c r="D8" s="0">
-        <v>62.808073479305861</v>
+        <v>63.770027468192794</v>
       </c>
       <c r="E8" s="0">
-        <v>-422.62268238268103</v>
+        <v>-422.55127956636477</v>
       </c>
     </row>
     <row r="9">
@@ -334,13 +454,13 @@
         <v>4.8187963762522656</v>
       </c>
       <c r="C9" s="0">
-        <v>174.42960780206641</v>
+        <v>178.42960780206596</v>
       </c>
       <c r="D9" s="0">
-        <v>27.278646525894835</v>
+        <v>26.951679451917265</v>
       </c>
       <c r="E9" s="0">
-        <v>-392.61594912051117</v>
+        <v>-392.53119513517862</v>
       </c>
     </row>
     <row r="10">
@@ -354,10 +474,10 @@
         <v>51.145410882910582</v>
       </c>
       <c r="D10" s="0">
-        <v>20.874631728955382</v>
+        <v>20.877557909462631</v>
       </c>
       <c r="E10" s="0">
-        <v>13.564891191586275</v>
+        <v>13.56212030498715</v>
       </c>
     </row>
     <row r="11">
@@ -371,10 +491,10 @@
         <v>60.145410882887603</v>
       </c>
       <c r="D11" s="0">
-        <v>40.012821618174208</v>
+        <v>39.933103123988694</v>
       </c>
       <c r="E11" s="0">
-        <v>0.033301100709225415</v>
+        <v>0.025201407907699428</v>
       </c>
     </row>
   </sheetData>
@@ -387,27 +507,27 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="14.42578125" customWidth="true"/>
-    <col min="2" max="2" width="11.5703125" customWidth="true"/>
-    <col min="3" max="3" width="11.7109375" customWidth="true"/>
+    <col min="2" max="2" width="20.42578125" customWidth="true"/>
+    <col min="3" max="3" width="16" customWidth="true"/>
     <col min="4" max="4" width="14.5703125" customWidth="true"/>
-    <col min="5" max="5" width="13.42578125" customWidth="true"/>
+    <col min="5" max="5" width="20.140625" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="0" t="s">
-        <v>35</v>
+        <v>75</v>
       </c>
       <c r="B1" s="0" t="s">
-        <v>36</v>
+        <v>76</v>
       </c>
       <c r="C1" s="0" t="s">
-        <v>37</v>
+        <v>77</v>
       </c>
       <c r="D1" s="0" t="s">
-        <v>38</v>
+        <v>78</v>
       </c>
       <c r="E1" s="0" t="s">
-        <v>39</v>
+        <v>79</v>
       </c>
     </row>
     <row r="2">
@@ -415,16 +535,16 @@
         <v>0.10000000000000001</v>
       </c>
       <c r="B2" s="0">
-        <v>0</v>
+        <v>0.99999999999988987</v>
       </c>
       <c r="C2" s="0">
         <v>199.99999999999997</v>
       </c>
       <c r="D2" s="0">
-        <v>3897.8249069377634</v>
+        <v>3843.8246050741532</v>
       </c>
       <c r="E2" s="0">
-        <v>0.28464869473299254</v>
+        <v>0.28854620970383765</v>
       </c>
     </row>
     <row r="3">
@@ -435,13 +555,13 @@
         <v>10.000000000000009</v>
       </c>
       <c r="C3" s="0">
-        <v>164.2969582681477</v>
+        <v>168.29695826814773</v>
       </c>
       <c r="D3" s="0">
-        <v>8.757753990432958</v>
+        <v>8.5922392241305996</v>
       </c>
       <c r="E3" s="0">
-        <v>1.1149743023903416</v>
+        <v>1.1163865109876174</v>
       </c>
     </row>
     <row r="4">
@@ -452,13 +572,13 @@
         <v>9.0000000000000071</v>
       </c>
       <c r="C4" s="0">
-        <v>138.56868145036927</v>
+        <v>147.56868145036927</v>
       </c>
       <c r="D4" s="0">
-        <v>20.892229562843113</v>
+        <v>20.736932917026234</v>
       </c>
       <c r="E4" s="0">
-        <v>-0.33658222341407873</v>
+        <v>-0.33833584309303522</v>
       </c>
     </row>
     <row r="5">
@@ -466,16 +586,16 @@
         <v>0.69999999999999996</v>
       </c>
       <c r="B5" s="0">
-        <v>0</v>
+        <v>0.99999999999988987</v>
       </c>
       <c r="C5" s="0">
         <v>119.59234523577733</v>
       </c>
       <c r="D5" s="0">
-        <v>8568.3973165452335</v>
+        <v>8623.2923247176295</v>
       </c>
       <c r="E5" s="0">
-        <v>-0.469269008190554</v>
+        <v>-0.46931437246742175</v>
       </c>
     </row>
     <row r="6">
@@ -489,10 +609,10 @@
         <v>51.59234523577738</v>
       </c>
       <c r="D6" s="0">
-        <v>21.232927380201929</v>
+        <v>21.228321554013498</v>
       </c>
       <c r="E6" s="0">
-        <v>0.25430249159849017</v>
+        <v>0.25432558704985753</v>
       </c>
     </row>
     <row r="7">
@@ -500,16 +620,16 @@
         <v>1.1000000000000001</v>
       </c>
       <c r="B7" s="0">
-        <v>0</v>
+        <v>0.99999999999988987</v>
       </c>
       <c r="C7" s="0">
-        <v>199.99999999999994</v>
+        <v>189.15442229709757</v>
       </c>
       <c r="D7" s="0">
-        <v>11229.646573354481</v>
+        <v>11138.073522368635</v>
       </c>
       <c r="E7" s="0">
-        <v>0.15464399356317843</v>
+        <v>0.15384278785205194</v>
       </c>
     </row>
     <row r="8">
@@ -520,13 +640,13 @@
         <v>6.9999999999992291</v>
       </c>
       <c r="C8" s="0">
-        <v>199.99999999999994</v>
+        <v>187.1544222970758</v>
       </c>
       <c r="D8" s="0">
-        <v>38.689538794276721</v>
+        <v>39.508087012641411</v>
       </c>
       <c r="E8" s="0">
-        <v>0.7803836857119284</v>
+        <v>0.7765818255538488</v>
       </c>
     </row>
     <row r="9">
@@ -537,13 +657,13 @@
         <v>9.9999999999988987</v>
       </c>
       <c r="C9" s="0">
-        <v>173.4296078020665</v>
+        <v>178.42960780206596</v>
       </c>
       <c r="D9" s="0">
-        <v>9.5888841692456399</v>
+        <v>9.2923959661009601</v>
       </c>
       <c r="E9" s="0">
-        <v>-0.83653688160829354</v>
+        <v>-0.84107626824954662</v>
       </c>
     </row>
     <row r="10">
@@ -551,16 +671,16 @@
         <v>1.7</v>
       </c>
       <c r="B10" s="0">
-        <v>0</v>
+        <v>0.99999999999988987</v>
       </c>
       <c r="C10" s="0">
-        <v>156.14541088289903</v>
+        <v>159.14541088289869</v>
       </c>
       <c r="D10" s="0">
-        <v>9573.6190460751423</v>
+        <v>9383.6423235937436</v>
       </c>
       <c r="E10" s="0">
-        <v>-0.72498914503889766</v>
+        <v>-0.72483016736645445</v>
       </c>
     </row>
     <row r="11">
@@ -571,13 +691,13 @@
         <v>8.9999999999990088</v>
       </c>
       <c r="C11" s="0">
-        <v>50.145410882888712</v>
+        <v>51.145410882888598</v>
       </c>
       <c r="D11" s="0">
-        <v>20.664977341532392</v>
+        <v>20.581459286420518</v>
       </c>
       <c r="E11" s="0">
-        <v>-0.0022863489690131081</v>
+        <v>-0.0017719479491269381</v>
       </c>
     </row>
   </sheetData>
